--- a/assets/data/excel/items.xlsx
+++ b/assets/data/excel/items.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,6 +1658,1230 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ITEM_PLUGIN_PROF_RANDOM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>随机职业插件</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Random Profession Plugin</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>plugin</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>professionPlugin</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>芯片合成时随机限定职业方向</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>{"type":"professionPlugin","profession":"random"}</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" t="n">
+        <v>99</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>["shop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ITEM_PLUGIN_RACE_SR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SR种族插件</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SR Race Plugin</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>plugin</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>racePlugin</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>芯片合成时限定SR级种族方向</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>{"type":"racePlugin","quality":"SR"}</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>80</v>
+      </c>
+      <c r="I26" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>99</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>["shop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ITEM_PLUGIN_ELEMENT_SR</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SR元素插件</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SR Element Plugin</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>plugin</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>elementPlugin</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>芯片合成时限定SR级元素方向</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>{"type":"elementPlugin","quality":"SR"}</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>80</v>
+      </c>
+      <c r="I27" t="n">
+        <v>15</v>
+      </c>
+      <c r="J27" t="n">
+        <v>99</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>["shop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ITEM_EXP_CHIP_SMALL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>初级芯片经验模块</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Basic Chip EXP Module</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>chipExp</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>芯片经验值+100</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>{"type":"chipExp","value":100}</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>999</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>["shop","zoneDrop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ITEM_EXP_CHIP_MEDIUM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>中级芯片经验模块</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mid Chip EXP Module</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>chipExp</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>芯片经验值+500</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>{"type":"chipExp","value":500}</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>120</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20</v>
+      </c>
+      <c r="J29" t="n">
+        <v>999</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>["shop","zoneDrop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ITEM_EXP_CHIP_LARGE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>高级芯片经验模块</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Advanced Chip EXP Module</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>chipExp</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>芯片经验值+2000</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>{"type":"chipExp","value":2000}</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>400</v>
+      </c>
+      <c r="I30" t="n">
+        <v>60</v>
+      </c>
+      <c r="J30" t="n">
+        <v>999</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>["shop","zoneDrop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ITEM_N_FRAGMENT_BOX</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N品质碎片宝箱</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>N Fragment Box</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>fragmentBox</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>打开获得随机N品质融合姬碎片x5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>{"type":"fragmentBox","quality":"N","count":5}</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="n">
+        <v>99</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>["quest","achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ITEM_UPGRADE_MATERIAL_LOW</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>初级强化材料</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Basic Upgrade Material</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>upgradeMaterial</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>融合姬升级消耗材料</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>{"type":"upgradeMaterial","tier":1}</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>999</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>["shop","zoneDrop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ITEM_UPGRADE_MATERIAL_MID</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>中级强化材料</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mid Upgrade Material</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>upgradeMaterial</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>融合姬升级消耗材料</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>{"type":"upgradeMaterial","tier":2}</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>80</v>
+      </c>
+      <c r="I33" t="n">
+        <v>15</v>
+      </c>
+      <c r="J33" t="n">
+        <v>999</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>["shop","zoneDrop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ITEM_CHIP_EXP_SMALL</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>芯片经验微粒</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chip EXP Dust</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>chipExp</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>芯片经验值+50</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>{"type":"chipExp","value":50}</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>15</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>999</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>["shop","zoneDrop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ITEM_CHIP_EXP_MEDIUM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>芯片经验结晶</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Chip EXP Crystal</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>chipExp</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>芯片经验值+300</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>{"type":"chipExp","value":300}</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>80</v>
+      </c>
+      <c r="I35" t="n">
+        <v>12</v>
+      </c>
+      <c r="J35" t="n">
+        <v>999</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>["shop","zoneDrop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ITEM_SKILL_UPGRADE_MATERIAL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>技能升级材料</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Skill Upgrade Material</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>skillUpgrade</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>技能升级消耗材料</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>{"type":"skillUpgrade"}</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" t="n">
+        <v>20</v>
+      </c>
+      <c r="J36" t="n">
+        <v>999</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>["shop","zoneDrop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ITEM_SOURCE_CORE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>源核</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Source Core</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>高级货币，用于抽卡和商店高级商品</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>{"type":"currency"}</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>9999</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>["quest","achievement","zoneDrop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PACK_NEWBIE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>新手礼包</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Newbie Pack</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>新手礼包，包含源核x200和随机SR融合姬碎片x10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>{"type":"pack","contents":[{"id":"ITEM_SOURCE_CORE","count":200},{"id":"FRAGMENT_SR_RANDOM","count":10}]}</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PACK_DAILY_DEAL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>每日特惠包</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Daily Deal Pack</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>每日特惠，包含源核x100和抗辐射药剂x2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>{"type":"pack","contents":[{"id":"ITEM_SOURCE_CORE","count":100},{"id":"ITEM_RAD_MEDICINE","count":2}]}</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>["shop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ITEM_PLUGIN_SSR</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SSR定向插件</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SSR Direction Plugin</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>plugin</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>directionPlugin</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>芯片合成时限定SSR品质方向</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>{"type":"directionPlugin","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>150</v>
+      </c>
+      <c r="I40" t="n">
+        <v>30</v>
+      </c>
+      <c r="J40" t="n">
+        <v>99</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>["shop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PACK_LIMITED_UP</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>限定UP礼包</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Limited UP Pack</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>pack</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>限定UP活动礼包，包含源核x500</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>{"type":"pack","contents":[{"id":"ITEM_SOURCE_CORE","count":500}]}</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>["shop"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GACHA_SINGLE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>单抽券</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Single Gacha Ticket</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>gachaTicket</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>可用于常驻融合姬池单抽1次</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>{"type":"gachaTicket","count":1}</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>99</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>["quest","achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>GACHA_TEN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>十连抽券</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ten Gacha Ticket</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>gachaTicket</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>可用于常驻融合姬池十连抽1次</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>{"type":"gachaTicket","count":10}</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>99</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>["quest","achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MINION_R</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>R品质融合姬碎片</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>R Minion Fragment</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>minionFragment</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>R品质融合姬通用碎片，用于碎片兑换</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>{"type":"minionFragment","quality":"R"}</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>999</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>["gachaDuplicate","quest"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MINION_SR</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SR品质融合姬碎片</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SR Minion Fragment</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>minionFragment</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SR品质融合姬通用碎片，用于碎片兑换</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>{"type":"minionFragment","quality":"SR"}</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" t="n">
+        <v>999</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>["gachaDuplicate","quest"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MINION_SSR</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SSR品质融合姬碎片</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SSR Minion Fragment</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>minionFragment</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SSR品质融合姬通用碎片，用于碎片兑换</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>{"type":"minionFragment","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>20</v>
+      </c>
+      <c r="J46" t="n">
+        <v>999</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>["gachaDuplicate","quest"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MINION_UR</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>UR品质融合姬碎片</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>UR Minion Fragment</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>minionFragment</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>UR品质融合姬通用碎片，用于碎片兑换</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>{"type":"minionFragment","quality":"UR"}</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>50</v>
+      </c>
+      <c r="J47" t="n">
+        <v>999</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>["gachaDuplicate","quest"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MYCELIUM_500</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>菌丝包裹</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Mycelium Bundle</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>包含500菌丝</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>{"type":"currency","currency":"mycelium","amount":500}</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>99</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>["shop"]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/data/excel/items.xlsx
+++ b/assets/data/excel/items.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2882,6 +2882,2709 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_002</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>废弃城区探索者</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Wasteland Explorer-R</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>探索废弃城区全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_002"}</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_003</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>荒野公路探索者</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Wasteland Explorer-R2</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>探索荒野公路全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_003"}</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_004</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>污染森林探索者</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Forest Explorer</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>探索污染森林全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_004"}</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_005</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>干涸河床探索者</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Riverbed Explorer</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>探索干涸河床全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_005"}</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_006</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>军事前哨探索者</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Outpost Explorer</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>探索军事前哨全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_006"}</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_007</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>沙漠绿洲探索者</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Oasis Explorer</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>探索沙漠绿洲全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_007"}</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_008</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>军事基地探索者</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Base Explorer</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>探索军事基地全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_008"}</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_009</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>地下设施探索者</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Underground Explorer</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>探索地下设施全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_009"}</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_010</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>辐射荒原探索者</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Radiation Explorer</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>探索辐射荒原全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_010"}</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_011</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>核心禁区探索者</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Core Explorer</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>探索核心禁区全部关卡的证明</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_011"}</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_012</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>废土开拓者</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wasteland Pioneer</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>探索全部10张地图的证明，SSR级称号</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_012"}</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_014</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>禁区征服者</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Zone Conqueror</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>通关全部10个Boss的证明，SSR级称号</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_014"}</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TITLE_EXP_015_LE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>星舰继承者</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Starship Heir</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>收集全部10个星舰零件的证明，LE级称号</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_EXP_015_LE"}</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TITLE_CMB_002</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>百战勇士</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Centurion</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>累计战斗胜利100场的证明</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_CMB_002"}</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TITLE_CMB_003</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>千胜将军</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Millennium Commander</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>累计战斗胜利1000场的证明，SSR级称号</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_CMB_003"}</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TITLE_CMB_005</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>以弱胜强</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Underdog Victor</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>以低于推荐战力通关关卡的证明</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_CMB_005"}</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TITLE_CMB_008</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Boss猎人</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Boss Hunter</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>击败10个不同Boss的证明，SSR级称号</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_CMB_008"}</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TITLE_CMB_010</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>闪电战</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Lightning War</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>3回合内结束战斗的证明</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_CMB_010"}</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TITLE_COL_003</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>收藏家</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Collector</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>收集50张不同融合姬卡的证明</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_COL_003"}</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TITLE_COL_004_LE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>全图鉴收集者</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Complete Collector</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>收集全部100张融合姬卡的证明，LE级称号</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_COL_004_LE"}</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TITLE_COL_006</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>五系齐聚</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Five Races United</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>同时拥有5种种族融合姬的证明</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_COL_006"}</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TITLE_COL_007</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>五素齐聚</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Five Elements United</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>同时拥有5种元素融合姬的证明</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_COL_007"}</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TITLE_GRW_003</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>精英培养师</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Elite Trainer</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>将任意融合姬培养至满级的证明</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_GRW_003"}</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TITLE_GRW_004</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>满级导师</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Max Level Mentor</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>拥有5张满级融合姬的证明，SSR级称号</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_GRW_004"}</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TITLE_GRW_009_LE</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>造物主</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Creator</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>完成一次主副卡融合品质提升的证明，LE级称号</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_GRW_009_LE"}</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TITLE_SOC_001</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>废土幸存者</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Wasteland Survivor</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>声望达到10级的证明</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SOC_001"}</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TITLE_SOC_002</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>废土探索者</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Wasteland Pathfinder</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>声望达到30级的证明</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SOC_002"}</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TITLE_SOC_003</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>废土先锋</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Wasteland Vanguard</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>声望达到50级的证明，SSR级称号</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SOC_003"}</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TITLE_SOC_004</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>废土传奇</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Wasteland Legend</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>声望达到75级的证明，SSR级称号</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SOC_004"}</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TITLE_SOC_005_LE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>废土至高者</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Wasteland Supreme</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>声望达到99级的证明，LE级称号</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SOC_005_LE"}</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TITLE_SPC_001</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>觉醒之人</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>The Awakened</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>完成新手引导的证明</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SPC_001"}</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TITLE_SPC_002</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>真相追寻者</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Truth Seeker</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>触发10个隐藏剧情事件的证明</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SPC_002"}</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TITLE_SPC_003</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>方舟发现者</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ark Discoverer</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>发现方舟核心的证明，SSR级称号</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SPC_003"}</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TITLE_SPC_004_LE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>终焉终结者</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Omega Terminator</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>通关终焉之地的证明，LE级称号</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SPC_004_LE"}</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TITLE_SPC_005</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>星舰继承者</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Starship Inheritor</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>收集全部星舰零件的证明，SSR级称号</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SPC_005"}</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TITLE_SPC_006</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>废土传说</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Wasteland Myth</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>完成全部成就的证明，LE级称号</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>{"type":"title","titleId":"TITLE_SPC_006"}</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FRAME_EXP_012</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>废土开拓者框</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Pioneer Frame</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>探索全部地图获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_EXP_012","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FRAME_EXP_014</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>禁区征服者框</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Conqueror Frame</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>通关全部Boss获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_EXP_014","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>FRAME_CMB_003</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>千胜将军框</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Commander Frame</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>千胜成就获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_CMB_003","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>FRAME_CMB_008</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Boss猎人框</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Hunter Frame</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Boss猎人成就获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_CMB_008","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>FRAME_COL_004</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>全图鉴收集者框</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Collector Frame</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>全图鉴成就获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_COL_004","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>FRAME_COL_009</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SSR品质收集框</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SSR Collection Frame</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>收集全部SSR卡获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_COL_009","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FRAME_COL_010</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>UR品质收集框</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>UR Collection Frame</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>收集全部UR卡获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_COL_010","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>FRAME_GRW_004</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>满级导师框</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Mentor Frame</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>满级导师成就获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_GRW_004","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FRAME_GRW_007</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>异化诞生框</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Mutation Frame</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>异化诞生成就获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_GRW_007","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>FRAME_SOC_003</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>废土先锋框</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Vanguard Frame</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>声望50级获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_SOC_003","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FRAME_SOC_004</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>废土传奇框</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Legend Frame</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>声望75级获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_SOC_004","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>FRAME_SOC_005</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>废土至高者框</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Supreme Frame</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>声望99级获得的LE级头像框</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_SOC_005","quality":"LE"}</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FRAME_SPC_003</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>方舟发现者框</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ark Frame</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>方舟发现成就获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_SPC_003","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FRAME_SPC_004</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>终焉终结者框</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Omega Frame</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>终焉通关获得的LE级头像框</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_SPC_004","quality":"LE"}</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>FRAME_SPC_005</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>星舰启航框</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Starship Frame</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>星舰启航成就获得的SSR级头像框</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_SPC_005","quality":"SSR"}</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>FRAME_SPC_006</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>废土传说框</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Myth Frame</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>全成就完成获得的LE级头像框</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_SPC_006","quality":"LE"}</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>["achievement"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FRAME_WEEKLY_ALL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>周常全勤框</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Weekly Perfect Frame</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>consumable</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>avatarFrame</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>完成全部每周任务获得的专属头像框</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>{"type":"avatarFrame","frameId":"FRAME_WEEKLY_ALL","quality":"SR"}</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>["weeklyQuest"]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
